--- a/artfynd/A 34050-2024 artfynd.xlsx
+++ b/artfynd/A 34050-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742782</v>
       </c>
       <c r="B2" t="n">
-        <v>90851</v>
+        <v>90954</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122742783</v>
       </c>
       <c r="B3" t="n">
-        <v>90802</v>
+        <v>90905</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 34050-2024 artfynd.xlsx
+++ b/artfynd/A 34050-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122742782</v>
+        <v>122742783</v>
       </c>
       <c r="B2" t="n">
-        <v>90954</v>
+        <v>90909</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>741182</v>
+        <v>741210</v>
       </c>
       <c r="R2" t="n">
         <v>7104879</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122742783</v>
+        <v>122742782</v>
       </c>
       <c r="B3" t="n">
-        <v>90905</v>
+        <v>90958</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741210</v>
+        <v>741182</v>
       </c>
       <c r="R3" t="n">
         <v>7104879</v>

--- a/artfynd/A 34050-2024 artfynd.xlsx
+++ b/artfynd/A 34050-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122742783</v>
+        <v>122742782</v>
       </c>
       <c r="B2" t="n">
-        <v>90909</v>
+        <v>90958</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>741210</v>
+        <v>741182</v>
       </c>
       <c r="R2" t="n">
         <v>7104879</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122742782</v>
+        <v>122742783</v>
       </c>
       <c r="B3" t="n">
-        <v>90958</v>
+        <v>90909</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741182</v>
+        <v>741210</v>
       </c>
       <c r="R3" t="n">
         <v>7104879</v>

--- a/artfynd/A 34050-2024 artfynd.xlsx
+++ b/artfynd/A 34050-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122742782</v>
+        <v>122742783</v>
       </c>
       <c r="B2" t="n">
-        <v>90958</v>
+        <v>90909</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>741182</v>
+        <v>741210</v>
       </c>
       <c r="R2" t="n">
         <v>7104879</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122742783</v>
+        <v>122742782</v>
       </c>
       <c r="B3" t="n">
-        <v>90909</v>
+        <v>90958</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741210</v>
+        <v>741182</v>
       </c>
       <c r="R3" t="n">
         <v>7104879</v>

--- a/artfynd/A 34050-2024 artfynd.xlsx
+++ b/artfynd/A 34050-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122742783</v>
+        <v>122742782</v>
       </c>
       <c r="B2" t="n">
-        <v>90909</v>
+        <v>90966</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>741210</v>
+        <v>741182</v>
       </c>
       <c r="R2" t="n">
         <v>7104879</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122742782</v>
+        <v>122742783</v>
       </c>
       <c r="B3" t="n">
-        <v>90958</v>
+        <v>90917</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741182</v>
+        <v>741210</v>
       </c>
       <c r="R3" t="n">
         <v>7104879</v>

--- a/artfynd/A 34050-2024 artfynd.xlsx
+++ b/artfynd/A 34050-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122742782</v>
+        <v>122742783</v>
       </c>
       <c r="B2" t="n">
-        <v>90966</v>
+        <v>90917</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>741182</v>
+        <v>741210</v>
       </c>
       <c r="R2" t="n">
         <v>7104879</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122742783</v>
+        <v>122742782</v>
       </c>
       <c r="B3" t="n">
-        <v>90917</v>
+        <v>90966</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741210</v>
+        <v>741182</v>
       </c>
       <c r="R3" t="n">
         <v>7104879</v>

--- a/artfynd/A 34050-2024 artfynd.xlsx
+++ b/artfynd/A 34050-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742783</v>
       </c>
       <c r="B2" t="n">
-        <v>90917</v>
+        <v>90920</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122742782</v>
       </c>
       <c r="B3" t="n">
-        <v>90966</v>
+        <v>90969</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 34050-2024 artfynd.xlsx
+++ b/artfynd/A 34050-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122742783</v>
+        <v>122742782</v>
       </c>
       <c r="B2" t="n">
-        <v>90920</v>
+        <v>90971</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>741210</v>
+        <v>741182</v>
       </c>
       <c r="R2" t="n">
         <v>7104879</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122742782</v>
+        <v>122742783</v>
       </c>
       <c r="B3" t="n">
-        <v>90969</v>
+        <v>90922</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741182</v>
+        <v>741210</v>
       </c>
       <c r="R3" t="n">
         <v>7104879</v>

--- a/artfynd/A 34050-2024 artfynd.xlsx
+++ b/artfynd/A 34050-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742782</v>
       </c>
       <c r="B2" t="n">
-        <v>91903</v>
+        <v>91906</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>122742783</v>
       </c>
       <c r="B3" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34050-2024 artfynd.xlsx
+++ b/artfynd/A 34050-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742782</v>
       </c>
       <c r="B2" t="n">
-        <v>91906</v>
+        <v>91912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>122742783</v>
       </c>
       <c r="B3" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34050-2024 artfynd.xlsx
+++ b/artfynd/A 34050-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742782</v>
       </c>
       <c r="B2" t="n">
-        <v>91912</v>
+        <v>91922</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>122742783</v>
       </c>
       <c r="B3" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34050-2024 artfynd.xlsx
+++ b/artfynd/A 34050-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742782</v>
       </c>
       <c r="B2" t="n">
-        <v>91922</v>
+        <v>91923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>122742783</v>
       </c>
       <c r="B3" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34050-2024 artfynd.xlsx
+++ b/artfynd/A 34050-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742782</v>
       </c>
       <c r="B2" t="n">
-        <v>91923</v>
+        <v>91924</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>122742783</v>
       </c>
       <c r="B3" t="n">
-        <v>91872</v>
+        <v>91873</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34050-2024 artfynd.xlsx
+++ b/artfynd/A 34050-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742782</v>
       </c>
       <c r="B2" t="n">
-        <v>91924</v>
+        <v>91926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>122742783</v>
       </c>
       <c r="B3" t="n">
-        <v>91873</v>
+        <v>91875</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34050-2024 artfynd.xlsx
+++ b/artfynd/A 34050-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742782</v>
       </c>
       <c r="B2" t="n">
-        <v>91926</v>
+        <v>91927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>122742783</v>
       </c>
       <c r="B3" t="n">
-        <v>91875</v>
+        <v>91876</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
